--- a/reports/cfb/CFB_Slate_2026-09-26.xlsx
+++ b/reports/cfb/CFB_Slate_2026-09-26.xlsx
@@ -12,6 +12,7 @@
     <sheet name="Weather" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Home Field" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Method &amp; Gaps" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="FCS" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3979,7 +3980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4271,40 +4272,130 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
+          <t>FCS: Chattanooga @ The Citadel</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>Shop</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>Citadel +11.5 (not +10.5), or Chattanooga -10.5 (not -11.5)</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>Two books are on different numbers: CHAT -11.5 (-111) and CIT +10.5 (-132). The market is 10.5/11.5, so one full point is available on whichever side you want. Pure shopping.</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>1u (FCS cap)</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>Low-Med</t>
+        </is>
+      </c>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>Both books converging to 11</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>FCS: Northern Arizona @ Montana State</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>Situational</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>No bet - but do NOT add altitude for Montana State</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>My own venue engine initially credited MSU with +1.0 of altitude by defaulting NAU to sea level. NAU plays in Flagstaff at ~6,900ft - HIGHER than Bozeman's 4,820. Real differential is -2,080ft, so the altitude edge is ZERO. MSU gets crowd only (+3.4). Most models would add a point that does not exist.</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>Nothing - this is a correction, not a bet</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
           <t>Money games (Pitt/FSU/Duke/SMU)</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>various</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D9" s="7" t="inlineStr">
         <is>
           <t>Structural</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>Favorite 2H under / team-total under - NOT the side</t>
         </is>
       </c>
-      <c r="F7" s="7" t="inlineStr">
+      <c r="F9" s="7" t="inlineStr">
         <is>
           <t>FBS-vs-FCS: big favorites empty the bench. Implied favorite team totals are Pitt 58.5, FSU 54.5, Duke 53.0, SMU 47.0. Those are 1st-half numbers being priced as full-game.</t>
         </is>
       </c>
-      <c r="G7" s="7" t="inlineStr">
+      <c r="G9" s="7" t="inlineStr">
         <is>
           <t>1u, thin data</t>
         </is>
       </c>
-      <c r="H7" s="7" t="inlineStr">
+      <c r="H9" s="7" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="I7" s="7" t="inlineStr">
+      <c r="I9" s="7" t="inlineStr">
         <is>
           <t>A backup QB who can actually play, or a starter left in for 4 quarters</t>
         </is>
@@ -5518,4 +5609,1704 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Z38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="46" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="19" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="19" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
+    <col width="11" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="11" customWidth="1" min="21" max="21"/>
+    <col width="12" customWidth="1" min="22" max="22"/>
+    <col width="13" customWidth="1" min="23" max="23"/>
+    <col width="46" customWidth="1" min="24" max="24"/>
+    <col width="37" customWidth="1" min="25" max="25"/>
+    <col width="46" customWidth="1" min="26" max="26"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Kick ET</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Conf</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Home Spread</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Favorite</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>PROJ SCORE (market-implied)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Proj Home</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Proj Away</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>P(fav win) %</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ML fair home %</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>ML fair home (Am)</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>ML hold %</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Total fair OVER %</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Total hold %</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Venue</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>HFA crowd</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>HFA altitude</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>HFA total</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Confidence</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Edge type</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>BEST BET</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Stake cap</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>North Dakota</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Indiana State</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>MVFC</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="F2" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>North Dakota</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Indiana State 21.0 - North Dakota 37.5</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>21</v>
+      </c>
+      <c r="K2" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="L2" t="n">
+        <v>82.7</v>
+      </c>
+      <c r="M2" t="n">
+        <v>8.32</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1103</v>
+      </c>
+      <c r="O2" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="P2" t="n">
+        <v>48.28</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>No bet - no independent number</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>1u (FCS data thin per sport-fcs.md)</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>UND favored on the road</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Furman</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Richmond</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>SoCon/CAA</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>-3</v>
+      </c>
+      <c r="F3" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Richmond</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>3</v>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Richmond 23.8 - Furman 20.7</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="K3" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="L3" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="M3" t="n">
+        <v>57.84</v>
+      </c>
+      <c r="N3" t="n">
+        <v>-137</v>
+      </c>
+      <c r="O3" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="V3" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>No bet - no independent number</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>1u (FCS data thin per sport-fcs.md)</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>FUR 2-2 (1-1 away), RICH 3-1 (2-0 home)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Northern Arizona</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Montana State</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Big Sky</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>-20.5</v>
+      </c>
+      <c r="F4" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Montana State</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Montana State 38.5 - Northern Arizona 18.0</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="K4" t="n">
+        <v>18</v>
+      </c>
+      <c r="L4" t="n">
+        <v>87.90000000000001</v>
+      </c>
+      <c r="M4" t="n">
+        <v>93.26000000000001</v>
+      </c>
+      <c r="N4" t="n">
+        <v>-1383</v>
+      </c>
+      <c r="O4" t="n">
+        <v>5.52</v>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Bobcat Stadium</t>
+        </is>
+      </c>
+      <c r="S4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="V4" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Situational</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>No bet - but do NOT add altitude for MSU here</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>1u (FCS data thin per sport-fcs.md)</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>NAU is a HIGH-ALTITUDE program (Flagstaff). MSU's altitude edge is neutralised.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Illinois State</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Northern Iowa</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>MVFC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="F5" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Illinois State</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Northern Iowa 19.5 - Illinois State 39.0</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="K5" t="n">
+        <v>39</v>
+      </c>
+      <c r="L5" t="n">
+        <v>86.7</v>
+      </c>
+      <c r="M5" t="n">
+        <v>8.52</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1073</v>
+      </c>
+      <c r="O5" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="V5" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>No bet - no independent number</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>1u (FCS data thin per sport-fcs.md)</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>ISU favored on the road; UNI-Dome is indoor - weather is a non-factor</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Southern Illinois</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Murray State</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>MVFC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Southern Illinois</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Murray State 18.5 - Southern Illinois 35.0</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="K6" t="n">
+        <v>35</v>
+      </c>
+      <c r="L6" t="n">
+        <v>82.7</v>
+      </c>
+      <c r="M6" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="N6" t="n">
+        <v>684</v>
+      </c>
+      <c r="O6" t="n">
+        <v>5.03</v>
+      </c>
+      <c r="P6" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="V6" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>No bet - no independent number</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>1u (FCS data thin per sport-fcs.md)</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>SIU favored on the road; SIU 2-2, MUR 1-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Maine</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Elon</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>CAA</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Elon</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Elon 25.0 - Maine 19.5</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>25</v>
+      </c>
+      <c r="K7" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="L7" t="n">
+        <v>62.3</v>
+      </c>
+      <c r="M7" t="n">
+        <v>65.36</v>
+      </c>
+      <c r="N7" t="n">
+        <v>-189</v>
+      </c>
+      <c r="O7" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="P7" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="V7" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>No bet - no independent number</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>1u (FCS data thin per sport-fcs.md)</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Southern</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Jackson State</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>SWAC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>-20.5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Jackson State</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Jackson State 39.0 - Southern 18.5</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>39</v>
+      </c>
+      <c r="K8" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="L8" t="n">
+        <v>87.90000000000001</v>
+      </c>
+      <c r="M8" t="n">
+        <v>90.98999999999999</v>
+      </c>
+      <c r="N8" t="n">
+        <v>-1010</v>
+      </c>
+      <c r="O8" t="n">
+        <v>5.03</v>
+      </c>
+      <c r="V8" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>No bet - no independent number</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>1u (FCS data thin per sport-fcs.md)</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>JSU 3-0 at home, SO 2-2 away. JSU opens SWAC play</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Western Carolina</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>East Tennessee St</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>SoCon</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="F9" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>East Tennessee St</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>East Tennessee St 32.5 - Western Carolina 31.0</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="K9" t="n">
+        <v>31</v>
+      </c>
+      <c r="L9" t="n">
+        <v>53.4</v>
+      </c>
+      <c r="M9" t="n">
+        <v>53.53</v>
+      </c>
+      <c r="N9" t="n">
+        <v>-115</v>
+      </c>
+      <c r="O9" t="n">
+        <v>5.12</v>
+      </c>
+      <c r="P9" t="n">
+        <v>51.03</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>5.12</v>
+      </c>
+      <c r="V9" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>No bet - no independent number</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>1u (FCS data thin per sport-fcs.md)</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>both 2-2; WCU 2-0 away, ETSU 2-1 home</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Chattanooga</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>The Citadel</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>SoCon</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="F10" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Chattanooga</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>The Citadel 18.0 - Chattanooga 29.5</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>18</v>
+      </c>
+      <c r="K10" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="L10" t="n">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="M10" t="n">
+        <v>22.51</v>
+      </c>
+      <c r="N10" t="n">
+        <v>344</v>
+      </c>
+      <c r="O10" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="P10" t="n">
+        <v>49.17</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="V10" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Shop</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Take Citadel +11.5 (not +10.5) or Chattanooga -10.5 (not -11.5)</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>1u (FCS data thin per sport-fcs.md)</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>SHOPPABLE: CHAT -11.5 (-111) at one book, CIT +10.5 (-132) at another - market is 10.5/11.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Stony Brook</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Fordham</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>CAA/Patriot</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="F11" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Stony Brook</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Fordham 21.0 - Stony Brook 31.5</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>21</v>
+      </c>
+      <c r="K11" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="L11" t="n">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="M11" t="n">
+        <v>20.74</v>
+      </c>
+      <c r="N11" t="n">
+        <v>382</v>
+      </c>
+      <c r="O11" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="P11" t="n">
+        <v>56.53</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="V11" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>No bet - under devigs FAIR at +130, offered +116 = -6.1% EV. Plus money is not value.</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>1u (FCS data thin per sport-fcs.md)</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>SBU favored on road. TOTAL JUICE IS LOPSIDED: over -144 / under +116</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Colgate</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Villanova</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Patriot/CAA</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>-10.5</v>
+      </c>
+      <c r="F12" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Villanova</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Villanova 30.0 - Colgate 19.5</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>30</v>
+      </c>
+      <c r="K12" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="L12" t="n">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="V12" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>No bet - no independent number</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>1u (FCS data thin per sport-fcs.md)</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>South Dakota</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Youngstown State</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>MVFC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="F13" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Youngstown State</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>Youngstown State 33.5 - South Dakota 32.0</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="K13" t="n">
+        <v>32</v>
+      </c>
+      <c r="L13" t="n">
+        <v>53.4</v>
+      </c>
+      <c r="V13" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Flag</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>No bet - 65.5 is the day's extreme; needs a number I don't have</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>1u (FCS data thin per sport-fcs.md)</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>HIGHEST TOTAL OF THE ENTIRE DAY, FBS or FCS</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Montana</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>UC Davis</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Big Sky</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>UC Davis</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>total not retrieved - no score projection published</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>55.7</v>
+      </c>
+      <c r="V14" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>No bet - no independent number</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>1u (FCS data thin per sport-fcs.md)</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>total NOT retrieved. Montana travels DOWN in elevation (3,200ft -&gt; ~50ft)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>IDENTIFIED BUT NO MARKET RETRIEVABLE - listed, never estimated:</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Cal Poly</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Eastern Washington</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Big Sky</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>no market retrieved</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Idaho State</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Southern Utah</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Big Sky</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>no market retrieved</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Portland State</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Weber State</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Big Sky</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>no market retrieved</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Utah Tech</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Northern Colorado</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Big Sky</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>no market retrieved</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>East Texas A&amp;M</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>McNeese</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Southland</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>no market retrieved</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Lamar</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Nicholls</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Southland</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>no market retrieved</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Southeastern Louisiana</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Northwestern State</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Southland</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>no market retrieved</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Sacramento State</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>UTRGV</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Southland/ind</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>no market retrieved</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Texas Southern</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Alcorn State</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>SWAC</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>no market retrieved</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Holy Cross</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Lafayette</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Patriot</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>no market retrieved</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Columbia</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Georgetown</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Ivy/Patriot</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>no market retrieved</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Lehigh</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Penn</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Patriot/Ivy</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>no market retrieved</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>UAlbany</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Princeton</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>CAA/Ivy</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>no market retrieved</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Monmouth</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Dartmouth</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>CAA/Ivy</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>no market retrieved</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Campbell</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Hampton</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>CAA</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>no market retrieved</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>VMI</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Samford</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>SoCon</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>no market retrieved</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Tennessee Tech</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Wofford</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>SoCon</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>no market retrieved</t>
+        </is>
+      </c>
+    </row>
+    <row r="34"/>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>FBS-vs-FCS money games are on the Slate tab: Bucknell @ Pittsburgh (-53.5); Central Arkansas @ Florida State (-45.5); William &amp; Mary @ Duke (-43.5); Missouri State @ SMU (-34.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>FCS stakes are capped at 1u per skills/sport-fcs.md - 63 scholarships vs 85, and the data is genuinely thin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Ivy and Pioneer leagues are NON-SCHOLARSHIP and are effectively a different sport. Princeton/Dartmouth/Penn/Georgetown games carry that caveat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Margin SD used for FCS win probability: 17.5 pts (a PRIOR, wider than the 16.5 used for FBS - FCS talent spread is larger).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>